--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.08888888888888889</v>
+        <v>0.07407407407407407</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.1197183098591549</v>
+        <v>0.09154929577464789</v>
       </c>
       <c r="D2">
-        <v>0.9124087591240876</v>
+        <v>0.9280575539568345</v>
       </c>
       <c r="E2">
         <v>135</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
